--- a/artfynd/A 59194-2024 artfynd.xlsx
+++ b/artfynd/A 59194-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121762038</v>
+        <v>121772838</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>56569</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -727,13 +731,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689817</v>
+        <v>689680</v>
       </c>
       <c r="R2" t="n">
-        <v>6664529</v>
+        <v>6664597</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,7 +775,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121772838</v>
+        <v>121762038</v>
       </c>
       <c r="B3" t="n">
-        <v>56569</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +805,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -846,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689680</v>
+        <v>689817</v>
       </c>
       <c r="R3" t="n">
-        <v>6664597</v>
+        <v>6664529</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,6 +889,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59194-2024 artfynd.xlsx
+++ b/artfynd/A 59194-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,6 +906,370 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121873465</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Malsättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>689586</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6664438</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mikael Sunnerstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Sunnerstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121873502</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56569</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Malsättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>689660</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6664461</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mikael Sunnerstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Sunnerstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121873481</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56569</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Malsättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>689638</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6664429</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mikael Sunnerstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Sunnerstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59194-2024 artfynd.xlsx
+++ b/artfynd/A 59194-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1270,6 +1270,124 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121881296</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57373</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Malsättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>689593</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6664412</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mikael Sunnerstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Sunnerstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59194-2024 artfynd.xlsx
+++ b/artfynd/A 59194-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121873465</v>
+        <v>121873481</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>56569</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,30 +924,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -961,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689586</v>
+        <v>689638</v>
       </c>
       <c r="R4" t="n">
-        <v>6664438</v>
+        <v>6664429</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1005,7 +1012,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1150,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121873481</v>
+        <v>121873465</v>
       </c>
       <c r="B6" t="n">
-        <v>56569</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,37 +1172,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1210,10 +1209,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>689638</v>
+        <v>689586</v>
       </c>
       <c r="R6" t="n">
-        <v>6664429</v>
+        <v>6664438</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1254,6 +1253,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1388,6 +1388,327 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121910450</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97067</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Malsättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>689895</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6664496</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mikael Sunnerstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Sunnerstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121910205</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97067</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Malsättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>689802</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6664508</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mikael Sunnerstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mikael Sunnerstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121909799</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97061</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Malsättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>689671</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6664385</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mikael Sunnerstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Sunnerstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59194-2024 artfynd.xlsx
+++ b/artfynd/A 59194-2024 artfynd.xlsx
@@ -1390,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121910450</v>
+        <v>121909799</v>
       </c>
       <c r="B8" t="n">
-        <v>97067</v>
+        <v>97061</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,38 +1406,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Malsättra, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>689895</v>
+        <v>689671</v>
       </c>
       <c r="R8" t="n">
-        <v>6664496</v>
+        <v>6664385</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1604,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121909799</v>
+        <v>121910450</v>
       </c>
       <c r="B10" t="n">
-        <v>97061</v>
+        <v>97067</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,38 +1620,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Malsättra, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>689671</v>
+        <v>689895</v>
       </c>
       <c r="R10" t="n">
-        <v>6664385</v>
+        <v>6664496</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 59194-2024 artfynd.xlsx
+++ b/artfynd/A 59194-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121772838</v>
+        <v>121762038</v>
       </c>
       <c r="B2" t="n">
-        <v>56569</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -731,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689680</v>
+        <v>689817</v>
       </c>
       <c r="R2" t="n">
-        <v>6664597</v>
+        <v>6664529</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -775,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121762038</v>
+        <v>121772838</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>56569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,35 +802,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -845,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689817</v>
+        <v>689680</v>
       </c>
       <c r="R3" t="n">
-        <v>6664529</v>
+        <v>6664597</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,7 +890,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1497,7 +1497,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121910205</v>
+        <v>121910450</v>
       </c>
       <c r="B9" t="n">
         <v>97067</v>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>689802</v>
+        <v>689895</v>
       </c>
       <c r="R9" t="n">
-        <v>6664508</v>
+        <v>6664496</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121910450</v>
+        <v>121910205</v>
       </c>
       <c r="B10" t="n">
         <v>97067</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>689895</v>
+        <v>689802</v>
       </c>
       <c r="R10" t="n">
-        <v>6664496</v>
+        <v>6664508</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 59194-2024 artfynd.xlsx
+++ b/artfynd/A 59194-2024 artfynd.xlsx
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121873481</v>
+        <v>121873465</v>
       </c>
       <c r="B4" t="n">
-        <v>56569</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,37 +924,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -968,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689638</v>
+        <v>689586</v>
       </c>
       <c r="R4" t="n">
-        <v>6664429</v>
+        <v>6664438</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1012,6 +1005,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1030,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121873502</v>
+        <v>121873481</v>
       </c>
       <c r="B5" t="n">
         <v>56569</v>
@@ -1073,11 +1067,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1094,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689660</v>
+        <v>689638</v>
       </c>
       <c r="R5" t="n">
-        <v>6664461</v>
+        <v>6664429</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1124,12 +1114,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121873465</v>
+        <v>121873502</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>56569</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,30 +1162,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1209,10 +1210,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>689586</v>
+        <v>689660</v>
       </c>
       <c r="R6" t="n">
-        <v>6664438</v>
+        <v>6664461</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1239,12 +1240,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,7 +1254,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121909799</v>
+        <v>121910450</v>
       </c>
       <c r="B8" t="n">
-        <v>97061</v>
+        <v>97067</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,38 +1406,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Malsättra, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>689671</v>
+        <v>689895</v>
       </c>
       <c r="R8" t="n">
-        <v>6664385</v>
+        <v>6664496</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121910450</v>
+        <v>121909799</v>
       </c>
       <c r="B9" t="n">
-        <v>97067</v>
+        <v>97061</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,38 +1513,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Malsättra, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>689895</v>
+        <v>689671</v>
       </c>
       <c r="R9" t="n">
-        <v>6664496</v>
+        <v>6664385</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 59194-2024 artfynd.xlsx
+++ b/artfynd/A 59194-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121762038</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>121772838</v>
       </c>
       <c r="B3" t="n">
-        <v>56569</v>
+        <v>56577</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121873481</v>
+        <v>121873502</v>
       </c>
       <c r="B5" t="n">
-        <v>56569</v>
+        <v>56577</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,7 +1067,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1084,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689638</v>
+        <v>689660</v>
       </c>
       <c r="R5" t="n">
-        <v>6664429</v>
+        <v>6664461</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1114,12 +1118,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121873502</v>
+        <v>121873481</v>
       </c>
       <c r="B6" t="n">
-        <v>56569</v>
+        <v>56577</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,11 +1193,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>689660</v>
+        <v>689638</v>
       </c>
       <c r="R6" t="n">
-        <v>6664461</v>
+        <v>6664429</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,7 +1275,7 @@
         <v>121881296</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121910450</v>
+        <v>121910205</v>
       </c>
       <c r="B8" t="n">
-        <v>97067</v>
+        <v>97085</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>689895</v>
+        <v>689802</v>
       </c>
       <c r="R8" t="n">
-        <v>6664496</v>
+        <v>6664508</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1500,7 +1500,7 @@
         <v>121909799</v>
       </c>
       <c r="B9" t="n">
-        <v>97061</v>
+        <v>97079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121910205</v>
+        <v>121910450</v>
       </c>
       <c r="B10" t="n">
-        <v>97067</v>
+        <v>97085</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>689802</v>
+        <v>689895</v>
       </c>
       <c r="R10" t="n">
-        <v>6664508</v>
+        <v>6664496</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 59194-2024 artfynd.xlsx
+++ b/artfynd/A 59194-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121762038</v>
+        <v>121772838</v>
       </c>
       <c r="B2" t="n">
-        <v>98131</v>
+        <v>56577</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -727,13 +731,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689817</v>
+        <v>689680</v>
       </c>
       <c r="R2" t="n">
-        <v>6664529</v>
+        <v>6664597</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,7 +775,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121772838</v>
+        <v>121762038</v>
       </c>
       <c r="B3" t="n">
-        <v>56577</v>
+        <v>98133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +805,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -846,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689680</v>
+        <v>689817</v>
       </c>
       <c r="R3" t="n">
-        <v>6664597</v>
+        <v>6664529</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,6 +889,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121873465</v>
+        <v>121873481</v>
       </c>
       <c r="B4" t="n">
-        <v>5173</v>
+        <v>56577</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,30 +924,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -961,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689586</v>
+        <v>689638</v>
       </c>
       <c r="R4" t="n">
-        <v>6664438</v>
+        <v>6664429</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1005,7 +1012,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1024,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121873502</v>
+        <v>121873465</v>
       </c>
       <c r="B5" t="n">
-        <v>56577</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,41 +1046,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1088,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689660</v>
+        <v>689586</v>
       </c>
       <c r="R5" t="n">
-        <v>6664461</v>
+        <v>6664438</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1118,12 +1113,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,6 +1127,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1150,7 +1146,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121873481</v>
+        <v>121873502</v>
       </c>
       <c r="B6" t="n">
         <v>56577</v>
@@ -1193,7 +1189,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>689638</v>
+        <v>689660</v>
       </c>
       <c r="R6" t="n">
-        <v>6664429</v>
+        <v>6664461</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1393,7 +1393,7 @@
         <v>121910205</v>
       </c>
       <c r="B8" t="n">
-        <v>97085</v>
+        <v>97087</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121909799</v>
+        <v>121910450</v>
       </c>
       <c r="B9" t="n">
-        <v>97079</v>
+        <v>97087</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,38 +1513,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Malsättra, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>689671</v>
+        <v>689895</v>
       </c>
       <c r="R9" t="n">
-        <v>6664385</v>
+        <v>6664496</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,113 +1601,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>121910450</v>
-      </c>
-      <c r="B10" t="n">
-        <v>97085</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Malsättra, Upl</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>689895</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6664496</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Östhammar</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Harg</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2024-12-27</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Mikael Sunnerstrand</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Mikael Sunnerstrand</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59194-2024 artfynd.xlsx
+++ b/artfynd/A 59194-2024 artfynd.xlsx
@@ -1390,7 +1390,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121910450</v>
+        <v>121910205</v>
       </c>
       <c r="B8" t="n">
         <v>97129</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>689895</v>
+        <v>689802</v>
       </c>
       <c r="R8" t="n">
-        <v>6664496</v>
+        <v>6664508</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1497,7 +1497,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121910205</v>
+        <v>121910450</v>
       </c>
       <c r="B9" t="n">
         <v>97129</v>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>689802</v>
+        <v>689895</v>
       </c>
       <c r="R9" t="n">
-        <v>6664508</v>
+        <v>6664496</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 59194-2024 artfynd.xlsx
+++ b/artfynd/A 59194-2024 artfynd.xlsx
@@ -1390,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121910205</v>
+        <v>121910450</v>
       </c>
       <c r="B8" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>689802</v>
+        <v>689895</v>
       </c>
       <c r="R8" t="n">
-        <v>6664508</v>
+        <v>6664496</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1497,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121910450</v>
+        <v>121910205</v>
       </c>
       <c r="B9" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>689895</v>
+        <v>689802</v>
       </c>
       <c r="R9" t="n">
-        <v>6664496</v>
+        <v>6664508</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
